--- a/tables/TableS3.xlsx
+++ b/tables/TableS3.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TableS4_gene_covariate_matrix" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TableS3_gene_covariate_matrix" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H115"/>
+  <dimension ref="A1:H105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -803,7 +804,6 @@
       <c r="F12" t="n">
         <v>46</v>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>9.699999999999999</v>
       </c>
@@ -1153,7 +1153,6 @@
       <c r="F23" t="n">
         <v>48.1</v>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>0</v>
       </c>
@@ -1183,7 +1182,6 @@
       <c r="F24" t="n">
         <v>46.3</v>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>0</v>
       </c>
@@ -1501,7 +1499,6 @@
       <c r="F34" t="n">
         <v>42.1</v>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
         <v>3.27</v>
       </c>
@@ -1531,7 +1528,6 @@
       <c r="F35" t="n">
         <v>41.8</v>
       </c>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>6.71</v>
       </c>
@@ -1593,7 +1589,6 @@
       <c r="F37" t="n">
         <v>67.40000000000001</v>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
         <v>6.32</v>
       </c>
@@ -1687,7 +1682,6 @@
       <c r="F40" t="n">
         <v>46.4</v>
       </c>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>2.59</v>
       </c>
@@ -1781,7 +1775,6 @@
       <c r="F43" t="n">
         <v>48.9</v>
       </c>
-      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
         <v>7.84</v>
       </c>
@@ -1821,7 +1814,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>H2AJ</t>
+          <t>H2BC13</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1835,23 +1828,22 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>3.6475</v>
+        <v>3.7569</v>
       </c>
       <c r="E45" t="n">
-        <v>4441</v>
+        <v>5714</v>
       </c>
       <c r="F45" t="n">
-        <v>51</v>
-      </c>
-      <c r="G45" t="inlineStr"/>
+        <v>52.1</v>
+      </c>
       <c r="H45" t="n">
-        <v>1.74</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>H2BC13</t>
+          <t>HMGA1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1865,23 +1857,22 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.7569</v>
+        <v>4.4532</v>
       </c>
       <c r="E46" t="n">
-        <v>5714</v>
+        <v>28395</v>
       </c>
       <c r="F46" t="n">
-        <v>52.1</v>
-      </c>
-      <c r="G46" t="inlineStr"/>
+        <v>42.1</v>
+      </c>
       <c r="H46" t="n">
-        <v>9.82</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>H3-7</t>
+          <t>HNRNPK</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1895,23 +1886,22 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>4.2881</v>
+        <v>4.0329</v>
       </c>
       <c r="E47" t="n">
-        <v>19412</v>
+        <v>10786</v>
       </c>
       <c r="F47" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="G47" t="inlineStr"/>
+        <v>40.2</v>
+      </c>
       <c r="H47" t="n">
-        <v>1.31</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>HMGA1</t>
+          <t>HNRNPU</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1925,23 +1915,22 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>4.4532</v>
+        <v>4.4217</v>
       </c>
       <c r="E48" t="n">
-        <v>28395</v>
+        <v>26403</v>
       </c>
       <c r="F48" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="G48" t="inlineStr"/>
+        <v>43.8</v>
+      </c>
       <c r="H48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>HNRNPK</t>
+          <t>HSPB1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1955,23 +1944,25 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4.0329</v>
+        <v>3.4574</v>
       </c>
       <c r="E49" t="n">
-        <v>10786</v>
+        <v>2867</v>
       </c>
       <c r="F49" t="n">
-        <v>40.2</v>
-      </c>
-      <c r="G49" t="inlineStr"/>
+        <v>62.7</v>
+      </c>
+      <c r="G49" t="n">
+        <v>2</v>
+      </c>
       <c r="H49" t="n">
-        <v>4.41</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>HNRNPU</t>
+          <t>HSPD1</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1985,23 +1976,25 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>4.4217</v>
+        <v>3.7909</v>
       </c>
       <c r="E50" t="n">
-        <v>26403</v>
+        <v>6179</v>
       </c>
       <c r="F50" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="G50" t="inlineStr"/>
+        <v>46.7</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1</v>
+      </c>
       <c r="H50" t="n">
-        <v>2</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>HSPB1</t>
+          <t>ILF3</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2015,25 +2008,22 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>3.4574</v>
+        <v>4.6014</v>
       </c>
       <c r="E51" t="n">
-        <v>2867</v>
+        <v>39936</v>
       </c>
       <c r="F51" t="n">
-        <v>62.7</v>
-      </c>
-      <c r="G51" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="H51" t="n">
-        <v>2</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>HSPD1</t>
+          <t>MFAP1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2047,25 +2037,25 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>3.7909</v>
+        <v>4.2139</v>
       </c>
       <c r="E52" t="n">
-        <v>6179</v>
+        <v>16366</v>
       </c>
       <c r="F52" t="n">
-        <v>46.7</v>
+        <v>44.9</v>
       </c>
       <c r="G52" t="n">
         <v>1</v>
       </c>
       <c r="H52" t="n">
-        <v>4.16</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ILF3</t>
+          <t>MSN</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2079,23 +2069,22 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>4.6014</v>
+        <v>4.2691</v>
       </c>
       <c r="E53" t="n">
-        <v>39936</v>
+        <v>18584</v>
       </c>
       <c r="F53" t="n">
-        <v>41</v>
-      </c>
-      <c r="G53" t="inlineStr"/>
+        <v>46.1</v>
+      </c>
       <c r="H53" t="n">
-        <v>6.53</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MFAP1</t>
+          <t>MYH9</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2109,25 +2098,25 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>4.2139</v>
+        <v>4.8244</v>
       </c>
       <c r="E54" t="n">
-        <v>16366</v>
+        <v>66742</v>
       </c>
       <c r="F54" t="n">
-        <v>44.9</v>
+        <v>40.5</v>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H54" t="n">
-        <v>2.04</v>
+        <v>14.19</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MSN</t>
+          <t>NCL</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2141,23 +2130,25 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>4.2691</v>
+        <v>4.1146</v>
       </c>
       <c r="E55" t="n">
-        <v>18584</v>
+        <v>13021</v>
       </c>
       <c r="F55" t="n">
-        <v>46.1</v>
-      </c>
-      <c r="G55" t="inlineStr"/>
+        <v>52</v>
+      </c>
+      <c r="G55" t="n">
+        <v>3</v>
+      </c>
       <c r="H55" t="n">
-        <v>5.17</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MYH9</t>
+          <t>PABPC1</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2171,25 +2162,22 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>4.8244</v>
+        <v>4.0401</v>
       </c>
       <c r="E56" t="n">
-        <v>66742</v>
+        <v>10968</v>
       </c>
       <c r="F56" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="G56" t="n">
-        <v>2</v>
+        <v>43.3</v>
       </c>
       <c r="H56" t="n">
-        <v>14.19</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>NCL</t>
+          <t>PCBP2</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2203,25 +2191,25 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>4.1146</v>
+        <v>4.3072</v>
       </c>
       <c r="E57" t="n">
-        <v>13021</v>
+        <v>20288</v>
       </c>
       <c r="F57" t="n">
-        <v>52</v>
+        <v>45.3</v>
       </c>
       <c r="G57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H57" t="n">
-        <v>2.92</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PABPC1</t>
+          <t>PDIA3</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2235,23 +2223,25 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>4.0401</v>
+        <v>4.154</v>
       </c>
       <c r="E58" t="n">
-        <v>10968</v>
+        <v>14255</v>
       </c>
       <c r="F58" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="G58" t="inlineStr"/>
+        <v>44.9</v>
+      </c>
+      <c r="G58" t="n">
+        <v>1.5</v>
+      </c>
       <c r="H58" t="n">
-        <v>4.77</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PCBP2</t>
+          <t>PDIA6</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2265,25 +2255,25 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>4.3072</v>
+        <v>4.1297</v>
       </c>
       <c r="E59" t="n">
-        <v>20288</v>
+        <v>13479</v>
       </c>
       <c r="F59" t="n">
-        <v>45.3</v>
+        <v>45.6</v>
       </c>
       <c r="G59" t="n">
         <v>1</v>
       </c>
       <c r="H59" t="n">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PDIA3</t>
+          <t>PNN</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2297,25 +2287,25 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>4.154</v>
+        <v>4.7004</v>
       </c>
       <c r="E60" t="n">
-        <v>14255</v>
+        <v>50162</v>
       </c>
       <c r="F60" t="n">
-        <v>44.9</v>
+        <v>43.4</v>
       </c>
       <c r="G60" t="n">
         <v>1.5</v>
       </c>
       <c r="H60" t="n">
-        <v>2.52</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PDIA6</t>
+          <t>PUF60</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2329,25 +2319,25 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>4.1297</v>
+        <v>4.805</v>
       </c>
       <c r="E61" t="n">
-        <v>13479</v>
+        <v>63833</v>
       </c>
       <c r="F61" t="n">
-        <v>45.6</v>
+        <v>40.4</v>
       </c>
       <c r="G61" t="n">
         <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>2.25</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PNN</t>
+          <t>RPL10A</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2361,25 +2351,25 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>4.7004</v>
+        <v>3.6468</v>
       </c>
       <c r="E62" t="n">
-        <v>50162</v>
+        <v>4434</v>
       </c>
       <c r="F62" t="n">
-        <v>43.4</v>
+        <v>47.2</v>
       </c>
       <c r="G62" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="H62" t="n">
-        <v>2.01</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PUF60</t>
+          <t>RPL14</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2393,25 +2383,25 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>4.805</v>
+        <v>3.6519</v>
       </c>
       <c r="E63" t="n">
-        <v>63833</v>
+        <v>4486</v>
       </c>
       <c r="F63" t="n">
-        <v>40.4</v>
+        <v>50.1</v>
       </c>
       <c r="G63" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="H63" t="n">
-        <v>6.65</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>RPL10A</t>
+          <t>RPL18</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2425,25 +2415,22 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>3.6468</v>
+        <v>3.6695</v>
       </c>
       <c r="E64" t="n">
-        <v>4434</v>
+        <v>4672</v>
       </c>
       <c r="F64" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="G64" t="n">
-        <v>3.5</v>
+        <v>46.4</v>
       </c>
       <c r="H64" t="n">
-        <v>2.34</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>RPL13</t>
+          <t>RPL27A</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2457,25 +2444,25 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>3.8396</v>
+        <v>3.7172</v>
       </c>
       <c r="E65" t="n">
-        <v>6912</v>
+        <v>5214</v>
       </c>
       <c r="F65" t="n">
-        <v>48.2</v>
+        <v>45.1</v>
       </c>
       <c r="G65" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="H65" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>RPL14</t>
+          <t>RPL7</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2489,25 +2476,25 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>3.6519</v>
+        <v>3.8439</v>
       </c>
       <c r="E66" t="n">
-        <v>4486</v>
+        <v>6981</v>
       </c>
       <c r="F66" t="n">
-        <v>50.1</v>
+        <v>46.3</v>
       </c>
       <c r="G66" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H66" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>RPL17</t>
+          <t>RPN1</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2521,25 +2508,25 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>3.9216</v>
+        <v>4.0518</v>
       </c>
       <c r="E67" t="n">
-        <v>8348</v>
+        <v>11267</v>
       </c>
       <c r="F67" t="n">
-        <v>47</v>
+        <v>42.7</v>
       </c>
       <c r="G67" t="n">
         <v>1</v>
       </c>
       <c r="H67" t="n">
-        <v>1.8</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>RPL18</t>
+          <t>RPS15</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2553,23 +2540,22 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>3.6695</v>
+        <v>3.772</v>
       </c>
       <c r="E68" t="n">
-        <v>4672</v>
+        <v>5916</v>
       </c>
       <c r="F68" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="G68" t="inlineStr"/>
+        <v>45.8</v>
+      </c>
       <c r="H68" t="n">
-        <v>2.52</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>RPL27A</t>
+          <t>RPS3A</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2583,25 +2569,25 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>3.7172</v>
+        <v>3.8562</v>
       </c>
       <c r="E69" t="n">
-        <v>5214</v>
+        <v>7181</v>
       </c>
       <c r="F69" t="n">
-        <v>45.1</v>
+        <v>42.1</v>
       </c>
       <c r="G69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H69" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>RPL7</t>
+          <t>RPS8</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2615,25 +2601,25 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>3.8439</v>
+        <v>3.7048</v>
       </c>
       <c r="E70" t="n">
-        <v>6981</v>
+        <v>5067</v>
       </c>
       <c r="F70" t="n">
-        <v>46.3</v>
+        <v>47.2</v>
       </c>
       <c r="G70" t="n">
         <v>1</v>
       </c>
       <c r="H70" t="n">
-        <v>2.08</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>RPL7A</t>
+          <t>RRBP1</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2647,25 +2633,25 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>3.9616</v>
+        <v>4.899</v>
       </c>
       <c r="E71" t="n">
-        <v>9154</v>
+        <v>79242</v>
       </c>
       <c r="F71" t="n">
-        <v>42.4</v>
+        <v>44.4</v>
       </c>
       <c r="G71" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H71" t="n">
         <v>2</v>
-      </c>
-      <c r="H71" t="n">
-        <v>1.84</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>RPN1</t>
+          <t>SEPTIN2</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2679,25 +2665,22 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>4.0518</v>
+        <v>4.3405</v>
       </c>
       <c r="E72" t="n">
-        <v>11267</v>
+        <v>21905</v>
       </c>
       <c r="F72" t="n">
-        <v>42.7</v>
-      </c>
-      <c r="G72" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="H72" t="n">
-        <v>2.23</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>RPS10P5</t>
+          <t>SERPINB9</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2711,23 +2694,22 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>4.2881</v>
+        <v>3.6142</v>
       </c>
       <c r="E73" t="n">
-        <v>19412</v>
+        <v>4113</v>
       </c>
       <c r="F73" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="G73" t="inlineStr"/>
+        <v>53.4</v>
+      </c>
       <c r="H73" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>RPS15</t>
+          <t>UBA52</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2741,23 +2723,25 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>3.772</v>
+        <v>3.4023</v>
       </c>
       <c r="E74" t="n">
-        <v>5916</v>
+        <v>2525</v>
       </c>
       <c r="F74" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="G74" t="inlineStr"/>
+        <v>53.2</v>
+      </c>
+      <c r="G74" t="n">
+        <v>2</v>
+      </c>
       <c r="H74" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>RPS3A</t>
+          <t>YBX1</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2771,337 +2755,333 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>3.8562</v>
+        <v>4.2883</v>
       </c>
       <c r="E75" t="n">
-        <v>7181</v>
+        <v>19424</v>
       </c>
       <c r="F75" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="G75" t="n">
-        <v>1</v>
+        <v>44.7</v>
       </c>
       <c r="H75" t="n">
-        <v>2.38</v>
+        <v>8.279999999999999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>RPS8</t>
+          <t>ADCY5</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>44 Non-Candidate</t>
+          <t>30 T2DM Control</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Pull-down</t>
+          <t>GWAS_literature</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>3.7048</v>
+        <v>5.7386</v>
       </c>
       <c r="E76" t="n">
-        <v>5067</v>
+        <v>547773</v>
       </c>
       <c r="F76" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="G76" t="n">
-        <v>1</v>
+        <v>36.4</v>
       </c>
       <c r="H76" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>RRBP1</t>
+          <t>APPL1</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>44 Non-Candidate</t>
+          <t>30 T2DM Control</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Pull-down</t>
+          <t>GWAS_literature</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>4.899</v>
+        <v>4.5732</v>
       </c>
       <c r="E77" t="n">
-        <v>79242</v>
+        <v>37425</v>
       </c>
       <c r="F77" t="n">
-        <v>44.4</v>
+        <v>42.6</v>
       </c>
       <c r="G77" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="H77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SEPTIN2</t>
+          <t>ARAP1</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>44 Non-Candidate</t>
+          <t>30 T2DM Control</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Pull-down</t>
+          <t>GWAS_literature</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>4.3405</v>
+        <v>5.0879</v>
       </c>
       <c r="E78" t="n">
-        <v>21905</v>
+        <v>122430</v>
       </c>
       <c r="F78" t="n">
-        <v>38</v>
-      </c>
-      <c r="G78" t="inlineStr"/>
+        <v>38.7</v>
+      </c>
+      <c r="G78" t="n">
+        <v>2</v>
+      </c>
       <c r="H78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SERPINB9</t>
+          <t>CAMK1D</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>44 Non-Candidate</t>
+          <t>30 T2DM Control</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Pull-down</t>
+          <t>GWAS_literature</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>3.6142</v>
+        <v>4.6818</v>
       </c>
       <c r="E79" t="n">
-        <v>4113</v>
+        <v>48057</v>
       </c>
       <c r="F79" t="n">
-        <v>53.4</v>
-      </c>
-      <c r="G79" t="inlineStr"/>
+        <v>38.1</v>
+      </c>
+      <c r="G79" t="n">
+        <v>1.5</v>
+      </c>
       <c r="H79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SERPINH1</t>
+          <t>CDKAL1</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>44 Non-Candidate</t>
+          <t>30 T2DM Control</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Pull-down</t>
+          <t>GWAS_literature</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>4.0789</v>
+        <v>5.8382</v>
       </c>
       <c r="E80" t="n">
-        <v>11993</v>
+        <v>688950</v>
       </c>
       <c r="F80" t="n">
-        <v>63.3</v>
+        <v>38.6</v>
       </c>
       <c r="G80" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="H80" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>TPM4</t>
+          <t>DGKB</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>44 Non-Candidate</t>
+          <t>30 T2DM Control</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Pull-down</t>
+          <t>GWAS_literature</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>4.1991</v>
+        <v>5.4174</v>
       </c>
       <c r="E81" t="n">
-        <v>15815</v>
+        <v>261485</v>
       </c>
       <c r="F81" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="G81" t="n">
-        <v>1</v>
+        <v>36.4</v>
       </c>
       <c r="H81" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>TUBB4B</t>
+          <t>DUSP8</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>44 Non-Candidate</t>
+          <t>30 T2DM Control</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Pull-down</t>
+          <t>GWAS_literature</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>3.6962</v>
+        <v>4.7873</v>
       </c>
       <c r="E82" t="n">
-        <v>4968</v>
+        <v>61280</v>
       </c>
       <c r="F82" t="n">
-        <v>50</v>
-      </c>
-      <c r="G82" t="inlineStr"/>
+        <v>36.1</v>
+      </c>
+      <c r="G82" t="n">
+        <v>1.5</v>
+      </c>
       <c r="H82" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>UBA52</t>
+          <t>FOXA2</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>44 Non-Candidate</t>
+          <t>30 T2DM Control</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Pull-down</t>
+          <t>GWAS_literature</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>3.4023</v>
+        <v>3.6008</v>
       </c>
       <c r="E83" t="n">
-        <v>2525</v>
+        <v>3988</v>
       </c>
       <c r="F83" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="G83" t="n">
-        <v>2</v>
+        <v>66.5</v>
       </c>
       <c r="H83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>VAT1</t>
+          <t>FTO</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>44 Non-Candidate</t>
+          <t>30 T2DM Control</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Pull-down</t>
+          <t>GWAS_literature</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>4.6951</v>
+        <v>5.3428</v>
       </c>
       <c r="E84" t="n">
-        <v>49551</v>
+        <v>220169</v>
       </c>
       <c r="F84" t="n">
-        <v>42.1</v>
+        <v>38.2</v>
       </c>
       <c r="G84" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="H84" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>YBX1</t>
+          <t>GCK</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>44 Non-Candidate</t>
+          <t>30 T2DM Control</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Pull-down</t>
+          <t>GWAS_literature</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>4.2883</v>
+        <v>4.5498</v>
       </c>
       <c r="E85" t="n">
-        <v>19424</v>
+        <v>35461</v>
       </c>
       <c r="F85" t="n">
-        <v>44.7</v>
-      </c>
-      <c r="G85" t="inlineStr"/>
+        <v>60.9</v>
+      </c>
+      <c r="G85" t="n">
+        <v>3</v>
+      </c>
       <c r="H85" t="n">
-        <v>8.279999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ADCY5</t>
+          <t>GCKR</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3115,15 +3095,17 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>5.7386</v>
+        <v>4.4371</v>
       </c>
       <c r="E86" t="n">
-        <v>547773</v>
+        <v>27360</v>
       </c>
       <c r="F86" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="G86" t="inlineStr"/>
+        <v>49.1</v>
+      </c>
+      <c r="G86" t="n">
+        <v>1</v>
+      </c>
       <c r="H86" t="n">
         <v>0</v>
       </c>
@@ -3131,7 +3113,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>APPL1</t>
+          <t>GRB14</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3145,13 +3127,13 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>4.5732</v>
+        <v>5.0265</v>
       </c>
       <c r="E87" t="n">
-        <v>37425</v>
+        <v>106288</v>
       </c>
       <c r="F87" t="n">
-        <v>42.6</v>
+        <v>42.2</v>
       </c>
       <c r="G87" t="n">
         <v>1</v>
@@ -3163,7 +3145,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ARAP1</t>
+          <t>HHEX</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3177,16 +3159,16 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>5.0879</v>
+        <v>4.4449</v>
       </c>
       <c r="E88" t="n">
-        <v>122430</v>
+        <v>27853</v>
       </c>
       <c r="F88" t="n">
-        <v>38.7</v>
+        <v>59.5</v>
       </c>
       <c r="G88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -3195,7 +3177,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CAMK1D</t>
+          <t>HMGA2</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3209,16 +3191,13 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>4.6818</v>
+        <v>4.8892</v>
       </c>
       <c r="E89" t="n">
-        <v>48057</v>
+        <v>77475</v>
       </c>
       <c r="F89" t="n">
-        <v>38.1</v>
-      </c>
-      <c r="G89" t="n">
-        <v>1.5</v>
+        <v>36.8</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -3227,7 +3206,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CDKAL1</t>
+          <t>HNF1A</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3241,16 +3220,13 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>5.8382</v>
+        <v>4.5022</v>
       </c>
       <c r="E90" t="n">
-        <v>688950</v>
+        <v>31786</v>
       </c>
       <c r="F90" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="G90" t="n">
-        <v>2.5</v>
+        <v>54.4</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3259,7 +3235,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>DGKB</t>
+          <t>HNF1B</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3273,15 +3249,14 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>5.4174</v>
+        <v>4.7719</v>
       </c>
       <c r="E91" t="n">
-        <v>261485</v>
+        <v>59144</v>
       </c>
       <c r="F91" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="G91" t="inlineStr"/>
+        <v>38.3</v>
+      </c>
       <c r="H91" t="n">
         <v>0</v>
       </c>
@@ -3289,7 +3264,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>DUSP8</t>
+          <t>JAZF1</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3303,16 +3278,16 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>4.7873</v>
+        <v>5.4632</v>
       </c>
       <c r="E92" t="n">
-        <v>61280</v>
+        <v>290504</v>
       </c>
       <c r="F92" t="n">
-        <v>36.1</v>
+        <v>41.4</v>
       </c>
       <c r="G92" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -3321,7 +3296,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>FOXA2</t>
+          <t>KCNJ11</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3335,15 +3310,17 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>3.6008</v>
+        <v>3.9834</v>
       </c>
       <c r="E93" t="n">
-        <v>3988</v>
+        <v>9625</v>
       </c>
       <c r="F93" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="G93" t="inlineStr"/>
+        <v>46.2</v>
+      </c>
+      <c r="G93" t="n">
+        <v>1.5</v>
+      </c>
       <c r="H93" t="n">
         <v>0</v>
       </c>
@@ -3351,7 +3328,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>FTO</t>
+          <t>KLF14</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3365,16 +3342,16 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>5.3428</v>
+        <v>3.9138</v>
       </c>
       <c r="E94" t="n">
-        <v>220169</v>
+        <v>8200</v>
       </c>
       <c r="F94" t="n">
-        <v>38.2</v>
+        <v>65</v>
       </c>
       <c r="G94" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -3383,7 +3360,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>GCK</t>
+          <t>MNX1</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3397,16 +3374,13 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>4.5498</v>
+        <v>3.8874</v>
       </c>
       <c r="E95" t="n">
-        <v>35461</v>
+        <v>7716</v>
       </c>
       <c r="F95" t="n">
-        <v>60.9</v>
-      </c>
-      <c r="G95" t="n">
-        <v>3</v>
+        <v>48.2</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3415,7 +3389,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>GCKR</t>
+          <t>PAM</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3429,13 +3403,13 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>4.4371</v>
+        <v>5.6652</v>
       </c>
       <c r="E96" t="n">
-        <v>27360</v>
+        <v>462588</v>
       </c>
       <c r="F96" t="n">
-        <v>49.1</v>
+        <v>36.6</v>
       </c>
       <c r="G96" t="n">
         <v>1</v>
@@ -3447,7 +3421,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>GRB14</t>
+          <t>PDX1</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3461,16 +3435,13 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>5.0265</v>
+        <v>3.9472</v>
       </c>
       <c r="E97" t="n">
-        <v>106288</v>
+        <v>8856</v>
       </c>
       <c r="F97" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="G97" t="n">
-        <v>1</v>
+        <v>61.8</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -3479,7 +3450,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>HHEX</t>
+          <t>PPARG</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3493,13 +3464,13 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>4.4449</v>
+        <v>5.6943</v>
       </c>
       <c r="E98" t="n">
-        <v>27853</v>
+        <v>494639</v>
       </c>
       <c r="F98" t="n">
-        <v>59.5</v>
+        <v>38.7</v>
       </c>
       <c r="G98" t="n">
         <v>1</v>
@@ -3511,7 +3482,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>HMGA2</t>
+          <t>PROX1</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3525,15 +3496,17 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>4.8892</v>
+        <v>4.6938</v>
       </c>
       <c r="E99" t="n">
-        <v>77475</v>
+        <v>49409</v>
       </c>
       <c r="F99" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="G99" t="inlineStr"/>
+        <v>36.5</v>
+      </c>
+      <c r="G99" t="n">
+        <v>1</v>
+      </c>
       <c r="H99" t="n">
         <v>0</v>
       </c>
@@ -3541,7 +3514,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>HNF1A</t>
+          <t>RREB1</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3555,15 +3528,17 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>4.5022</v>
+        <v>5.2486</v>
       </c>
       <c r="E100" t="n">
-        <v>31786</v>
+        <v>177238</v>
       </c>
       <c r="F100" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="G100" t="inlineStr"/>
+        <v>44</v>
+      </c>
+      <c r="G100" t="n">
+        <v>1</v>
+      </c>
       <c r="H100" t="n">
         <v>0</v>
       </c>
@@ -3571,7 +3546,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>HNF1B</t>
+          <t>SLC16A11</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3585,15 +3560,17 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>4.7719</v>
+        <v>4.162</v>
       </c>
       <c r="E101" t="n">
-        <v>59144</v>
+        <v>14520</v>
       </c>
       <c r="F101" t="n">
-        <v>38.3</v>
-      </c>
-      <c r="G101" t="inlineStr"/>
+        <v>36.5</v>
+      </c>
+      <c r="G101" t="n">
+        <v>1</v>
+      </c>
       <c r="H101" t="n">
         <v>0</v>
       </c>
@@ -3601,7 +3578,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>JAZF1</t>
+          <t>SLC30A8</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3615,16 +3592,13 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>5.4632</v>
+        <v>5.042</v>
       </c>
       <c r="E102" t="n">
-        <v>290504</v>
+        <v>110156</v>
       </c>
       <c r="F102" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="G102" t="n">
-        <v>2</v>
+        <v>40.2</v>
       </c>
       <c r="H102" t="n">
         <v>0</v>
@@ -3633,7 +3607,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>KCNJ11</t>
+          <t>ST6GAL1</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3647,13 +3621,13 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>3.9834</v>
+        <v>4.9695</v>
       </c>
       <c r="E103" t="n">
-        <v>9625</v>
+        <v>93218</v>
       </c>
       <c r="F103" t="n">
-        <v>46.2</v>
+        <v>37.7</v>
       </c>
       <c r="G103" t="n">
         <v>1.5</v>
@@ -3665,7 +3639,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>KLF14</t>
+          <t>TCF7L2</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3679,16 +3653,13 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>3.9138</v>
+        <v>5.3507</v>
       </c>
       <c r="E104" t="n">
-        <v>8200</v>
+        <v>224243</v>
       </c>
       <c r="F104" t="n">
-        <v>65</v>
-      </c>
-      <c r="G104" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3697,7 +3668,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MNX1</t>
+          <t>TSPAN8</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3711,329 +3682,47 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>3.8874</v>
+        <v>4.9671</v>
       </c>
       <c r="E105" t="n">
-        <v>7716</v>
+        <v>92696</v>
       </c>
       <c r="F105" t="n">
-        <v>48.2</v>
-      </c>
-      <c r="G105" t="inlineStr"/>
+        <v>42</v>
+      </c>
       <c r="H105" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>PAM</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>30 T2DM Control</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>GWAS_literature</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>5.6652</v>
-      </c>
-      <c r="E106" t="n">
-        <v>462588</v>
-      </c>
-      <c r="F106" t="n">
-        <v>36.6</v>
-      </c>
-      <c r="G106" t="n">
-        <v>1</v>
-      </c>
-      <c r="H106" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>PDX1</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>30 T2DM Control</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>GWAS_literature</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>3.9472</v>
-      </c>
-      <c r="E107" t="n">
-        <v>8856</v>
-      </c>
-      <c r="F107" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>PPARG</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>30 T2DM Control</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>GWAS_literature</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>5.6943</v>
-      </c>
-      <c r="E108" t="n">
-        <v>494639</v>
-      </c>
-      <c r="F108" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="G108" t="n">
-        <v>1</v>
-      </c>
-      <c r="H108" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>PROX1</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>30 T2DM Control</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>GWAS_literature</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>4.6938</v>
-      </c>
-      <c r="E109" t="n">
-        <v>49409</v>
-      </c>
-      <c r="F109" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="G109" t="n">
-        <v>1</v>
-      </c>
-      <c r="H109" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>RREB1</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>30 T2DM Control</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>GWAS_literature</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>5.2486</v>
-      </c>
-      <c r="E110" t="n">
-        <v>177238</v>
-      </c>
-      <c r="F110" t="n">
-        <v>44</v>
-      </c>
-      <c r="G110" t="n">
-        <v>1</v>
-      </c>
-      <c r="H110" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>SLC16A11</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>30 T2DM Control</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>GWAS_literature</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>4.162</v>
-      </c>
-      <c r="E111" t="n">
-        <v>14520</v>
-      </c>
-      <c r="F111" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="G111" t="n">
-        <v>1</v>
-      </c>
-      <c r="H111" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>SLC30A8</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>30 T2DM Control</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>GWAS_literature</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>5.042</v>
-      </c>
-      <c r="E112" t="n">
-        <v>110156</v>
-      </c>
-      <c r="F112" t="n">
-        <v>40.2</v>
-      </c>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>ST6GAL1</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>30 T2DM Control</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>GWAS_literature</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>4.9695</v>
-      </c>
-      <c r="E113" t="n">
-        <v>93218</v>
-      </c>
-      <c r="F113" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="G113" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H113" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>TCF7L2</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>30 T2DM Control</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>GWAS_literature</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>5.3507</v>
-      </c>
-      <c r="E114" t="n">
-        <v>224243</v>
-      </c>
-      <c r="F114" t="n">
-        <v>36</v>
-      </c>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>TSPAN8</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>30 T2DM Control</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>GWAS_literature</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>4.9671</v>
-      </c>
-      <c r="E115" t="n">
-        <v>92696</v>
-      </c>
-      <c r="F115" t="n">
-        <v>42</v>
-      </c>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="n">
-        <v>0</v>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="120" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Supplementary Table S3. Gene Covariate Matrix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Complete covariate data for all 104+ genes across three groups (30 HOTAIR Candidates, 44+ Non-Candidates, 30 T2DM Controls). Columns: Gene symbol, Group, Source (Pull-down/Literature/GWAS), log10 gene length (bp), Length_bp, GC content (%), Mean eQTL SNP count per gene (model SNPs), and Pull-down Unused score for candidate genes.</t>
+        </is>
       </c>
     </row>
   </sheetData>
